--- a/public/قالب-الشركات.xlsx
+++ b/public/قالب-الشركات.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D04B02-5096-40B2-AB3A-C9A22CBC66EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2A5B29-6DF2-40FA-BD05-D38D1440DE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>م</t>
   </si>
@@ -53,13 +53,16 @@
     <t>مبلغ الإعفاء</t>
   </si>
   <si>
-    <t>سعر الجريدة</t>
-  </si>
-  <si>
     <t>عدد التحويلات</t>
   </si>
   <si>
     <t>عدد التأشيرات</t>
+  </si>
+  <si>
+    <t>رسوم النشر في صحف الأعمال</t>
+  </si>
+  <si>
+    <t>تاريخ انتهاء السجل التجاري</t>
   </si>
 </sst>
 </file>
@@ -495,21 +498,22 @@
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="11" width="12" customWidth="1"/>
-    <col min="12" max="15" width="15" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="29.109375" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="12" width="12" customWidth="1"/>
+    <col min="13" max="16" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -529,34 +533,43 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1048559:G1048576" xr:uid="{E9AEE86F-3E9E-4052-9F4F-FE02404C1C21}">
+      <formula1>43831</formula1>
+      <formula2>45292</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
